--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 38602-2025 artfynd.xlsx
+++ b/artfynd/A 38602-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128306041</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
